--- a/artfynd/A 4501-2023 artfynd.xlsx
+++ b/artfynd/A 4501-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303144</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4501-2023 artfynd.xlsx
+++ b/artfynd/A 4501-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303144</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4501-2023 artfynd.xlsx
+++ b/artfynd/A 4501-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303144</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4501-2023 artfynd.xlsx
+++ b/artfynd/A 4501-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303144</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4501-2023 artfynd.xlsx
+++ b/artfynd/A 4501-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131303144</v>
       </c>
       <c r="B2" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 4501-2023 artfynd.xlsx
+++ b/artfynd/A 4501-2023 artfynd.xlsx
@@ -1122,45 +1122,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133221095</v>
+        <v>133221120</v>
       </c>
       <c r="B6" t="n">
-        <v>99130</v>
+        <v>91918</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Högkälen, Ång</t>
+          <t>Holmstrand, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585246</v>
+        <v>585176</v>
       </c>
       <c r="R6" t="n">
-        <v>7014781</v>
+        <v>7014888</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,45 +1229,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133221120</v>
+        <v>133221095</v>
       </c>
       <c r="B7" t="n">
-        <v>91918</v>
+        <v>99130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Holmstrand, Ång</t>
+          <t>Högkälen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585176</v>
+        <v>585246</v>
       </c>
       <c r="R7" t="n">
-        <v>7014888</v>
+        <v>7014781</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2299,32 +2299,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133221110</v>
+        <v>133221115</v>
       </c>
       <c r="B17" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
         <v>585171</v>
       </c>
       <c r="R17" t="n">
-        <v>7014865</v>
+        <v>7014876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,32 +2406,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133221115</v>
+        <v>133221110</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>80398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,7 +2444,7 @@
         <v>585171</v>
       </c>
       <c r="R18" t="n">
-        <v>7014876</v>
+        <v>7014865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 4501-2023 artfynd.xlsx
+++ b/artfynd/A 4501-2023 artfynd.xlsx
@@ -1657,7 +1657,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133221096</v>
+        <v>133221106</v>
       </c>
       <c r="B11" t="n">
         <v>99130</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585265</v>
+        <v>585165</v>
       </c>
       <c r="R11" t="n">
-        <v>7014794</v>
+        <v>7014844</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,7 +1764,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133221106</v>
+        <v>133221096</v>
       </c>
       <c r="B12" t="n">
         <v>99130</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585165</v>
+        <v>585265</v>
       </c>
       <c r="R12" t="n">
-        <v>7014844</v>
+        <v>7014794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2299,32 +2299,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133221115</v>
+        <v>133221110</v>
       </c>
       <c r="B17" t="n">
-        <v>91918</v>
+        <v>80398</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
         <v>585171</v>
       </c>
       <c r="R17" t="n">
-        <v>7014876</v>
+        <v>7014865</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,32 +2406,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133221110</v>
+        <v>133221115</v>
       </c>
       <c r="B18" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,7 +2444,7 @@
         <v>585171</v>
       </c>
       <c r="R18" t="n">
-        <v>7014865</v>
+        <v>7014876</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 4501-2023 artfynd.xlsx
+++ b/artfynd/A 4501-2023 artfynd.xlsx
@@ -1657,7 +1657,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133221106</v>
+        <v>133221096</v>
       </c>
       <c r="B11" t="n">
         <v>99130</v>
@@ -1692,10 +1692,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585165</v>
+        <v>585265</v>
       </c>
       <c r="R11" t="n">
-        <v>7014844</v>
+        <v>7014794</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,7 +1764,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133221096</v>
+        <v>133221106</v>
       </c>
       <c r="B12" t="n">
         <v>99130</v>
@@ -1799,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585265</v>
+        <v>585165</v>
       </c>
       <c r="R12" t="n">
-        <v>7014794</v>
+        <v>7014844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2299,32 +2299,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133221110</v>
+        <v>133221115</v>
       </c>
       <c r="B17" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2337,7 +2337,7 @@
         <v>585171</v>
       </c>
       <c r="R17" t="n">
-        <v>7014865</v>
+        <v>7014876</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,32 +2406,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133221115</v>
+        <v>133221110</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>80398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2444,7 +2444,7 @@
         <v>585171</v>
       </c>
       <c r="R18" t="n">
-        <v>7014876</v>
+        <v>7014865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2620,10 +2620,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133221117</v>
+        <v>133221098</v>
       </c>
       <c r="B20" t="n">
-        <v>92217</v>
+        <v>79333</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585174</v>
+        <v>585213</v>
       </c>
       <c r="R20" t="n">
-        <v>7014885</v>
+        <v>7014770</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2727,10 +2727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133221098</v>
+        <v>133221117</v>
       </c>
       <c r="B21" t="n">
-        <v>79333</v>
+        <v>92217</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2738,21 +2738,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2762,10 +2762,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585213</v>
+        <v>585174</v>
       </c>
       <c r="R21" t="n">
-        <v>7014770</v>
+        <v>7014885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
